--- a/grupos/3ALCM - Estadisticos 20221.xlsx
+++ b/grupos/3ALCM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="179">
   <si>
     <t>Materia</t>
   </si>
@@ -206,6 +206,9 @@
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
+    <t>Caballero Rosas María Teresa</t>
+  </si>
+  <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
@@ -213,9 +216,6 @@
   </si>
   <si>
     <t>Castro Vasquez Julieta</t>
-  </si>
-  <si>
-    <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
     <t>Ángel Martínez Noe Cristobal</t>
@@ -1058,19 +1058,19 @@
         <v>9</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -1097,13 +1097,13 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V4">
         <v>9</v>
       </c>
       <c r="W4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>8</v>
@@ -1135,19 +1135,19 @@
         <v>10</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1177,13 +1177,13 @@
         <v>7</v>
       </c>
       <c r="V5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>10</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>10</v>
@@ -1212,19 +1212,19 @@
         <v>9</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1248,7 +1248,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U6">
         <v>5</v>
@@ -1257,10 +1257,10 @@
         <v>8</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>9</v>
@@ -1289,19 +1289,19 @@
         <v>10</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1328,13 +1328,13 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>9</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X7">
         <v>10</v>
@@ -1366,19 +1366,19 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1405,13 +1405,13 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V8">
         <v>9</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X8">
         <v>10</v>
@@ -1443,19 +1443,19 @@
         <v>6</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1479,16 +1479,16 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U9">
         <v>5</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X9">
         <v>5</v>
@@ -1520,19 +1520,19 @@
         <v>9</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1556,7 +1556,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U10">
         <v>5</v>
@@ -1565,7 +1565,7 @@
         <v>8</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>8</v>
@@ -1597,19 +1597,19 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1636,16 +1636,16 @@
         <v>9</v>
       </c>
       <c r="U11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>9</v>
@@ -1674,19 +1674,19 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1713,13 +1713,13 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V12">
         <v>8</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>9</v>
@@ -1751,19 +1751,19 @@
         <v>10</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1787,7 +1787,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U13">
         <v>7</v>
@@ -1796,7 +1796,7 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>10</v>
@@ -1810,7 +1810,7 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C14">
         <v>5</v>
@@ -1828,19 +1828,19 @@
         <v>8</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1864,7 +1864,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U14">
         <v>5</v>
@@ -1873,10 +1873,10 @@
         <v>7</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y14">
         <v>8</v>
@@ -1905,19 +1905,19 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1941,19 +1941,19 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U15">
         <v>5</v>
       </c>
       <c r="V15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y15">
         <v>6</v>
@@ -1982,19 +1982,19 @@
         <v>9</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -2018,16 +2018,16 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U16">
         <v>5</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>9</v>
@@ -2059,19 +2059,19 @@
         <v>9</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -2095,7 +2095,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U17">
         <v>7</v>
@@ -2104,10 +2104,10 @@
         <v>8</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y17">
         <v>9</v>
@@ -2118,7 +2118,7 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C18">
         <v>8</v>
@@ -2136,19 +2136,19 @@
         <v>10</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -2172,7 +2172,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U18">
         <v>8</v>
@@ -2213,19 +2213,19 @@
         <v>7</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -2249,19 +2249,19 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U19">
         <v>5</v>
       </c>
       <c r="V19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>7</v>
@@ -2290,19 +2290,19 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2326,7 +2326,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U20">
         <v>5</v>
@@ -2335,7 +2335,7 @@
         <v>7</v>
       </c>
       <c r="W20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X20">
         <v>9</v>
@@ -2367,19 +2367,19 @@
         <v>9</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2403,7 +2403,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U21">
         <v>7</v>
@@ -2412,10 +2412,10 @@
         <v>8</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>9</v>
@@ -2444,19 +2444,19 @@
         <v>10</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2521,19 +2521,19 @@
         <v>10</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -2566,7 +2566,7 @@
         <v>10</v>
       </c>
       <c r="W23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X23">
         <v>10</v>
@@ -2598,19 +2598,19 @@
         <v>8</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2634,7 +2634,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U24">
         <v>7</v>
@@ -2643,10 +2643,10 @@
         <v>8</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y24">
         <v>8</v>
@@ -2675,19 +2675,19 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2752,19 +2752,19 @@
         <v>9</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2794,7 +2794,7 @@
         <v>9</v>
       </c>
       <c r="V26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W26">
         <v>10</v>
@@ -2829,19 +2829,19 @@
         <v>9</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -2874,7 +2874,7 @@
         <v>8</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X27">
         <v>9</v>
@@ -2906,19 +2906,19 @@
         <v>9</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -2945,16 +2945,16 @@
         <v>9</v>
       </c>
       <c r="U28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V28">
         <v>8</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>9</v>
@@ -2983,19 +2983,19 @@
         <v>9</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -3019,7 +3019,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U29">
         <v>6</v>
@@ -3028,7 +3028,7 @@
         <v>10</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X29">
         <v>10</v>
@@ -3060,19 +3060,19 @@
         <v>9</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -3096,19 +3096,19 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V30">
         <v>9</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>9</v>
@@ -3137,19 +3137,19 @@
         <v>9</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -3173,10 +3173,10 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>8</v>
@@ -3185,7 +3185,7 @@
         <v>10</v>
       </c>
       <c r="X31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y31">
         <v>9</v>
@@ -3214,19 +3214,19 @@
         <v>8</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -3250,7 +3250,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U32">
         <v>6</v>
@@ -3259,7 +3259,7 @@
         <v>8</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X32">
         <v>10</v>
@@ -3291,19 +3291,19 @@
         <v>10</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -3330,13 +3330,13 @@
         <v>10</v>
       </c>
       <c r="U33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V33">
         <v>10</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X33">
         <v>10</v>
@@ -3368,19 +3368,19 @@
         <v>10</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
         <v>-1</v>
@@ -3407,7 +3407,7 @@
         <v>10</v>
       </c>
       <c r="U34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V34">
         <v>9</v>
@@ -3445,19 +3445,19 @@
         <v>10</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M35">
         <v>-1</v>
@@ -3481,10 +3481,10 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V35">
         <v>8</v>
@@ -3522,19 +3522,19 @@
         <v>10</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M36">
         <v>-1</v>
@@ -3558,7 +3558,7 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U36">
         <v>5</v>
@@ -3567,10 +3567,10 @@
         <v>9</v>
       </c>
       <c r="W36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y36">
         <v>10</v>
@@ -3599,19 +3599,19 @@
         <v>7</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M37">
         <v>-1</v>
@@ -3635,19 +3635,19 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U37">
         <v>5</v>
       </c>
       <c r="V37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y37">
         <v>7</v>
@@ -3676,19 +3676,19 @@
         <v>10</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M38">
         <v>-1</v>
@@ -3721,10 +3721,10 @@
         <v>8</v>
       </c>
       <c r="W38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y38">
         <v>10</v>
@@ -3753,19 +3753,19 @@
         <v>8</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M39">
         <v>-1</v>
@@ -3789,7 +3789,7 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U39">
         <v>5</v>
@@ -3798,10 +3798,10 @@
         <v>7</v>
       </c>
       <c r="W39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y39">
         <v>8</v>
@@ -3830,19 +3830,19 @@
         <v>8</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M40">
         <v>-1</v>
@@ -3866,19 +3866,19 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W40">
         <v>10</v>
       </c>
       <c r="X40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y40">
         <v>8</v>
@@ -3907,19 +3907,19 @@
         <v>9</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M41">
         <v>-1</v>
@@ -3943,19 +3943,19 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V41">
         <v>8</v>
       </c>
       <c r="W41">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y41">
         <v>9</v>
@@ -3984,19 +3984,19 @@
         <v>10</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M42">
         <v>-1</v>
@@ -4020,7 +4020,7 @@
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U42">
         <v>6</v>
@@ -4029,7 +4029,7 @@
         <v>8</v>
       </c>
       <c r="W42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X42">
         <v>10</v>
@@ -4061,19 +4061,19 @@
         <v>7</v>
       </c>
       <c r="H43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M43">
         <v>-1</v>
@@ -4097,16 +4097,16 @@
         <v>-1</v>
       </c>
       <c r="T43">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U43">
         <v>7</v>
       </c>
       <c r="V43">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W43">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X43">
         <v>7</v>
@@ -4177,19 +4177,19 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F2">
-        <v>70.73</v>
+        <v>51.22</v>
       </c>
       <c r="G2">
-        <v>29.27</v>
+        <v>48.78</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4200,7 +4200,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
@@ -4209,19 +4209,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>90.23999999999999</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="G3">
-        <v>9.76</v>
+        <v>7.32</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4232,7 +4232,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
@@ -4241,19 +4241,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>97.56</v>
+        <v>95.12</v>
       </c>
       <c r="G4">
-        <v>2.44</v>
+        <v>4.88</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4264,7 +4264,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
@@ -4273,19 +4273,19 @@
         <v>41</v>
       </c>
       <c r="D5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>100</v>
+        <v>97.56</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4296,7 +4296,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
@@ -4317,7 +4317,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4349,7 +4349,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5124,7 +5124,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5156,16 +5156,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920255</v>
+        <v>21330051920282</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="D2" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -5179,19 +5179,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920255</v>
+        <v>21330051920282</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="D3" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
         <v>62</v>
@@ -5202,22 +5202,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920081</v>
+        <v>21330051920251</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D4" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5225,16 +5225,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920081</v>
+        <v>21330051920253</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D5" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -5248,16 +5248,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920282</v>
+        <v>21330051920256</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="D6" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -5271,22 +5271,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920282</v>
+        <v>21330051920257</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="D7" t="s">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5294,16 +5294,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920286</v>
+        <v>21330051920081</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="D8" t="s">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -5317,22 +5317,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920286</v>
+        <v>21330051920263</v>
       </c>
       <c r="B9" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="D9" t="s">
-        <v>175</v>
+        <v>142</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5340,16 +5340,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920253</v>
+        <v>21330051920264</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D10" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -5363,16 +5363,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920256</v>
+        <v>21330051920267</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" t="s">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -5386,16 +5383,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920262</v>
+        <v>21330051920088</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D12" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -5409,16 +5406,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920264</v>
+        <v>21330051920358</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D13" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
@@ -5432,16 +5429,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920088</v>
+        <v>21330051920361</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C14" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="D14" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
@@ -5455,16 +5452,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920358</v>
+        <v>21330051920362</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="C15" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D15" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="E15" t="s">
         <v>6</v>
@@ -5478,22 +5475,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920268</v>
+        <v>21330051920280</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C16" t="s">
-        <v>124</v>
+        <v>77</v>
       </c>
       <c r="D16" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -5501,16 +5498,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920280</v>
+        <v>21330051920284</v>
       </c>
       <c r="B17" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C17" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="D17" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E17" t="s">
         <v>6</v>
@@ -5542,6 +5539,52 @@
         <v>61</v>
       </c>
       <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>21330051920286</v>
+      </c>
+      <c r="B19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" t="s">
+        <v>175</v>
+      </c>
+      <c r="E19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>20330051920358</v>
+      </c>
+      <c r="B20" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" t="s">
+        <v>136</v>
+      </c>
+      <c r="D20" t="s">
+        <v>176</v>
+      </c>
+      <c r="E20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" t="s">
+        <v>61</v>
+      </c>
+      <c r="G20">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ALCM - Estadisticos 20221.xlsx
+++ b/grupos/3ALCM - Estadisticos 20221.xlsx
@@ -212,10 +212,10 @@
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
+    <t>Castro Vasquez Julieta</t>
+  </si>
+  <si>
     <t>Rivera Cruz Ezequiel</t>
-  </si>
-  <si>
-    <t>Castro Vasquez Julieta</t>
   </si>
   <si>
     <t>Ángel Martínez Noe Cristobal</t>
@@ -1073,7 +1073,7 @@
         <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1150,7 +1150,7 @@
         <v>9</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1227,7 +1227,7 @@
         <v>8</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1304,7 +1304,7 @@
         <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1381,7 +1381,7 @@
         <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1458,7 +1458,7 @@
         <v>5</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1494,7 +1494,7 @@
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1535,7 +1535,7 @@
         <v>8</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1612,7 +1612,7 @@
         <v>8</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1648,7 +1648,7 @@
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1689,7 +1689,7 @@
         <v>8</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1766,7 +1766,7 @@
         <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1843,7 +1843,7 @@
         <v>8</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1920,7 +1920,7 @@
         <v>5</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1956,7 +1956,7 @@
         <v>5</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1997,7 +1997,7 @@
         <v>8</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -2074,7 +2074,7 @@
         <v>9</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2151,7 +2151,7 @@
         <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2228,7 +2228,7 @@
         <v>7</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2264,7 +2264,7 @@
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2305,7 +2305,7 @@
         <v>8</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2382,7 +2382,7 @@
         <v>9</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2459,7 +2459,7 @@
         <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2536,7 +2536,7 @@
         <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2613,7 +2613,7 @@
         <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2649,7 +2649,7 @@
         <v>8</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2690,7 +2690,7 @@
         <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2767,7 +2767,7 @@
         <v>10</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2803,7 +2803,7 @@
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2844,7 +2844,7 @@
         <v>8</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2880,7 +2880,7 @@
         <v>9</v>
       </c>
       <c r="Y27">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2921,7 +2921,7 @@
         <v>8</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2957,7 +2957,7 @@
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2998,7 +2998,7 @@
         <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -3034,7 +3034,7 @@
         <v>10</v>
       </c>
       <c r="Y29">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3075,7 +3075,7 @@
         <v>8</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3111,7 +3111,7 @@
         <v>9</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3152,7 +3152,7 @@
         <v>8</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3229,7 +3229,7 @@
         <v>10</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3265,7 +3265,7 @@
         <v>10</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3306,7 +3306,7 @@
         <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3383,7 +3383,7 @@
         <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3460,7 +3460,7 @@
         <v>9</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3537,7 +3537,7 @@
         <v>8</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3614,7 +3614,7 @@
         <v>7</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3691,7 +3691,7 @@
         <v>7</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3768,7 +3768,7 @@
         <v>7</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3804,7 +3804,7 @@
         <v>6</v>
       </c>
       <c r="Y39">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3845,7 +3845,7 @@
         <v>7</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3922,7 +3922,7 @@
         <v>8</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -3958,7 +3958,7 @@
         <v>8</v>
       </c>
       <c r="Y41">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -3999,7 +3999,7 @@
         <v>9</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -4076,7 +4076,7 @@
         <v>7</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N43">
         <v>-1</v>
@@ -4112,7 +4112,7 @@
         <v>7</v>
       </c>
       <c r="Y43">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -4264,7 +4264,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
@@ -4285,7 +4285,7 @@
         <v>2.44</v>
       </c>
       <c r="H5">
-        <v>9.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4296,7 +4296,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
@@ -4305,19 +4305,19 @@
         <v>41</v>
       </c>
       <c r="D6">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>100</v>
+        <v>97.56</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>

--- a/grupos/3ALCM - Estadisticos 20221.xlsx
+++ b/grupos/3ALCM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="179">
   <si>
     <t>Materia</t>
   </si>
@@ -1076,7 +1076,7 @@
         <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -1088,7 +1088,7 @@
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -1106,7 +1106,7 @@
         <v>8</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y4">
         <v>9</v>
@@ -1153,7 +1153,7 @@
         <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -1165,7 +1165,7 @@
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -1183,7 +1183,7 @@
         <v>10</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>10</v>
@@ -1230,7 +1230,7 @@
         <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -1242,13 +1242,13 @@
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>5</v>
@@ -1307,7 +1307,7 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -1319,7 +1319,7 @@
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1337,7 +1337,7 @@
         <v>10</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>10</v>
@@ -1384,7 +1384,7 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -1396,7 +1396,7 @@
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1414,7 +1414,7 @@
         <v>10</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>10</v>
@@ -1461,7 +1461,7 @@
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -1473,7 +1473,7 @@
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1538,7 +1538,7 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -1550,7 +1550,7 @@
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1615,7 +1615,7 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -1627,7 +1627,7 @@
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1692,7 +1692,7 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -1704,7 +1704,7 @@
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1722,7 +1722,7 @@
         <v>8</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>10</v>
@@ -1769,7 +1769,7 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -1781,13 +1781,13 @@
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S13">
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U13">
         <v>7</v>
@@ -1799,7 +1799,7 @@
         <v>8</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>10</v>
@@ -1846,7 +1846,7 @@
         <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -1858,13 +1858,13 @@
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S14">
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>5</v>
@@ -1876,7 +1876,7 @@
         <v>10</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>8</v>
@@ -1923,7 +1923,7 @@
         <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -1935,13 +1935,13 @@
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U15">
         <v>5</v>
@@ -1953,7 +1953,7 @@
         <v>8</v>
       </c>
       <c r="X15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y15">
         <v>7</v>
@@ -2000,7 +2000,7 @@
         <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -2012,13 +2012,13 @@
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U16">
         <v>5</v>
@@ -2030,7 +2030,7 @@
         <v>8</v>
       </c>
       <c r="X16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>9</v>
@@ -2077,7 +2077,7 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -2089,7 +2089,7 @@
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -2154,7 +2154,7 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -2166,7 +2166,7 @@
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -2184,7 +2184,7 @@
         <v>10</v>
       </c>
       <c r="X18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y18">
         <v>10</v>
@@ -2231,7 +2231,7 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -2243,7 +2243,7 @@
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2308,7 +2308,7 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -2320,13 +2320,13 @@
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U20">
         <v>5</v>
@@ -2338,7 +2338,7 @@
         <v>8</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y20">
         <v>10</v>
@@ -2385,7 +2385,7 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -2397,13 +2397,13 @@
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S21">
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U21">
         <v>7</v>
@@ -2415,7 +2415,7 @@
         <v>10</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>9</v>
@@ -2462,7 +2462,7 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -2474,7 +2474,7 @@
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2539,7 +2539,7 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
         <v>-1</v>
@@ -2551,7 +2551,7 @@
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -2616,7 +2616,7 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
         <v>-1</v>
@@ -2628,7 +2628,7 @@
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2693,7 +2693,7 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
         <v>-1</v>
@@ -2705,7 +2705,7 @@
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
         <v>-1</v>
@@ -2770,7 +2770,7 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
         <v>-1</v>
@@ -2782,7 +2782,7 @@
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -2847,7 +2847,7 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
         <v>-1</v>
@@ -2859,13 +2859,13 @@
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U27">
         <v>7</v>
@@ -2924,7 +2924,7 @@
         <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
         <v>-1</v>
@@ -2936,7 +2936,7 @@
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
         <v>-1</v>
@@ -3001,7 +3001,7 @@
         <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O29">
         <v>-1</v>
@@ -3013,13 +3013,13 @@
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U29">
         <v>6</v>
@@ -3031,7 +3031,7 @@
         <v>10</v>
       </c>
       <c r="X29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y29">
         <v>10</v>
@@ -3078,7 +3078,7 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
         <v>-1</v>
@@ -3090,7 +3090,7 @@
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
         <v>-1</v>
@@ -3155,7 +3155,7 @@
         <v>9</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O31">
         <v>-1</v>
@@ -3167,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
         <v>-1</v>
@@ -3232,7 +3232,7 @@
         <v>9</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O32">
         <v>-1</v>
@@ -3244,13 +3244,13 @@
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S32">
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U32">
         <v>6</v>
@@ -3309,7 +3309,7 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
         <v>-1</v>
@@ -3321,7 +3321,7 @@
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
         <v>-1</v>
@@ -3386,7 +3386,7 @@
         <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
         <v>-1</v>
@@ -3398,7 +3398,7 @@
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
         <v>-1</v>
@@ -3463,7 +3463,7 @@
         <v>9</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O35">
         <v>-1</v>
@@ -3475,13 +3475,13 @@
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S35">
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U35">
         <v>7</v>
@@ -3493,7 +3493,7 @@
         <v>10</v>
       </c>
       <c r="X35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y35">
         <v>10</v>
@@ -3540,7 +3540,7 @@
         <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
         <v>-1</v>
@@ -3552,7 +3552,7 @@
         <v>-1</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S36">
         <v>-1</v>
@@ -3617,7 +3617,7 @@
         <v>7</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O37">
         <v>-1</v>
@@ -3629,13 +3629,13 @@
         <v>-1</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S37">
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U37">
         <v>5</v>
@@ -3694,7 +3694,7 @@
         <v>9</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O38">
         <v>-1</v>
@@ -3706,13 +3706,13 @@
         <v>-1</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S38">
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U38">
         <v>5</v>
@@ -3724,7 +3724,7 @@
         <v>8</v>
       </c>
       <c r="X38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y38">
         <v>10</v>
@@ -3771,7 +3771,7 @@
         <v>9</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O39">
         <v>-1</v>
@@ -3783,7 +3783,7 @@
         <v>-1</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S39">
         <v>-1</v>
@@ -3801,7 +3801,7 @@
         <v>7</v>
       </c>
       <c r="X39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y39">
         <v>9</v>
@@ -3848,7 +3848,7 @@
         <v>8</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O40">
         <v>-1</v>
@@ -3860,13 +3860,13 @@
         <v>-1</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S40">
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U40">
         <v>5</v>
@@ -3878,7 +3878,7 @@
         <v>10</v>
       </c>
       <c r="X40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y40">
         <v>8</v>
@@ -3925,7 +3925,7 @@
         <v>10</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O41">
         <v>-1</v>
@@ -3937,13 +3937,13 @@
         <v>-1</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S41">
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U41">
         <v>5</v>
@@ -3955,7 +3955,7 @@
         <v>9</v>
       </c>
       <c r="X41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y41">
         <v>10</v>
@@ -4002,7 +4002,7 @@
         <v>9</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O42">
         <v>-1</v>
@@ -4014,13 +4014,13 @@
         <v>-1</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S42">
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U42">
         <v>6</v>
@@ -4032,7 +4032,7 @@
         <v>9</v>
       </c>
       <c r="X42">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y42">
         <v>10</v>
@@ -4079,7 +4079,7 @@
         <v>8</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O43">
         <v>-1</v>
@@ -4091,7 +4091,7 @@
         <v>-1</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S43">
         <v>-1</v>
@@ -4241,19 +4241,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>95.12</v>
+        <v>97.56</v>
       </c>
       <c r="G4">
-        <v>4.88</v>
+        <v>2.44</v>
       </c>
       <c r="H4">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4317,7 +4317,7 @@
         <v>2.44</v>
       </c>
       <c r="H6">
-        <v>9.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5124,7 +5124,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5156,16 +5156,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920282</v>
+        <v>21330051920262</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="D2" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -5179,16 +5179,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920282</v>
+        <v>21330051920262</v>
       </c>
       <c r="B3" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="D3" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -5202,16 +5202,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920251</v>
+        <v>21330051920282</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="D4" t="s">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -5225,22 +5225,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920253</v>
+        <v>21330051920282</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="D5" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5248,16 +5248,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920256</v>
+        <v>21330051920251</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D6" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -5271,16 +5271,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920257</v>
+        <v>21330051920253</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D7" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
@@ -5294,16 +5294,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920081</v>
+        <v>21330051920256</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -5317,16 +5317,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920263</v>
+        <v>21330051920257</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -5340,16 +5340,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920264</v>
+        <v>21330051920081</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D10" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -5363,13 +5363,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920267</v>
+        <v>21330051920263</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>82</v>
+      </c>
+      <c r="C11" t="s">
+        <v>119</v>
       </c>
       <c r="D11" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -5383,16 +5386,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920088</v>
+        <v>21330051920264</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D12" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -5406,16 +5409,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920358</v>
+        <v>21330051920267</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
-      </c>
-      <c r="C13" t="s">
-        <v>123</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
@@ -5429,16 +5429,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920361</v>
+        <v>21330051920088</v>
       </c>
       <c r="B14" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="D14" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
@@ -5452,16 +5452,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920362</v>
+        <v>21330051920358</v>
       </c>
       <c r="B15" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D15" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="E15" t="s">
         <v>6</v>
@@ -5475,16 +5475,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920280</v>
+        <v>21330051920361</v>
       </c>
       <c r="B16" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" t="s">
         <v>103</v>
       </c>
-      <c r="C16" t="s">
-        <v>77</v>
-      </c>
       <c r="D16" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
@@ -5498,16 +5498,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920284</v>
+        <v>21330051920362</v>
       </c>
       <c r="B17" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C17" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D17" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E17" t="s">
         <v>6</v>
@@ -5521,16 +5521,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920285</v>
+        <v>21330051920280</v>
       </c>
       <c r="B18" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="D18" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E18" t="s">
         <v>6</v>
@@ -5544,16 +5544,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920286</v>
+        <v>21330051920284</v>
       </c>
       <c r="B19" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>135</v>
       </c>
       <c r="D19" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E19" t="s">
         <v>6</v>
@@ -5567,16 +5567,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920358</v>
+        <v>21330051920285</v>
       </c>
       <c r="B20" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C20" t="s">
-        <v>136</v>
+        <v>94</v>
       </c>
       <c r="D20" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E20" t="s">
         <v>6</v>
@@ -5585,6 +5585,52 @@
         <v>61</v>
       </c>
       <c r="G20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>21330051920286</v>
+      </c>
+      <c r="B21" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" t="s">
+        <v>93</v>
+      </c>
+      <c r="D21" t="s">
+        <v>175</v>
+      </c>
+      <c r="E21" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21" t="s">
+        <v>61</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>20330051920358</v>
+      </c>
+      <c r="B22" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" t="s">
+        <v>136</v>
+      </c>
+      <c r="D22" t="s">
+        <v>176</v>
+      </c>
+      <c r="E22" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" t="s">
+        <v>61</v>
+      </c>
+      <c r="G22">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ALCM - Estadisticos 20221.xlsx
+++ b/grupos/3ALCM - Estadisticos 20221.xlsx
@@ -1085,7 +1085,7 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
         <v>6</v>
@@ -1162,7 +1162,7 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
         <v>6</v>
@@ -1239,7 +1239,7 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
         <v>8</v>
@@ -1316,7 +1316,7 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>8</v>
@@ -1393,7 +1393,7 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
         <v>9</v>
@@ -1411,7 +1411,7 @@
         <v>9</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -1470,7 +1470,7 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R9">
         <v>5</v>
@@ -1488,7 +1488,7 @@
         <v>5</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X9">
         <v>5</v>
@@ -1547,7 +1547,7 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
         <v>7</v>
@@ -1624,7 +1624,7 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>9</v>
@@ -1701,7 +1701,7 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
         <v>8</v>
@@ -1778,7 +1778,7 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
         <v>6</v>
@@ -1855,7 +1855,7 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
         <v>6</v>
@@ -1873,7 +1873,7 @@
         <v>7</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>8</v>
@@ -1932,7 +1932,7 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
         <v>8</v>
@@ -2009,7 +2009,7 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
         <v>8</v>
@@ -2086,7 +2086,7 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>9</v>
@@ -2163,7 +2163,7 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>8</v>
@@ -2240,7 +2240,7 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
         <v>7</v>
@@ -2317,7 +2317,7 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
         <v>7</v>
@@ -2394,7 +2394,7 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
         <v>9</v>
@@ -2412,7 +2412,7 @@
         <v>8</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X21">
         <v>8</v>
@@ -2471,7 +2471,7 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>9</v>
@@ -2548,7 +2548,7 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>9</v>
@@ -2625,7 +2625,7 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>9</v>
@@ -2702,7 +2702,7 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>9</v>
@@ -2779,7 +2779,7 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
         <v>9</v>
@@ -2856,7 +2856,7 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>9</v>
@@ -2933,7 +2933,7 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
         <v>9</v>
@@ -3010,7 +3010,7 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>8</v>
@@ -3087,7 +3087,7 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
         <v>8</v>
@@ -3164,7 +3164,7 @@
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R31">
         <v>9</v>
@@ -3241,7 +3241,7 @@
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
         <v>9</v>
@@ -3318,7 +3318,7 @@
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>10</v>
@@ -3395,7 +3395,7 @@
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>10</v>
@@ -3472,7 +3472,7 @@
         <v>-1</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R35">
         <v>9</v>
@@ -3549,7 +3549,7 @@
         <v>-1</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R36">
         <v>8</v>
@@ -3626,7 +3626,7 @@
         <v>-1</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R37">
         <v>7</v>
@@ -3644,7 +3644,7 @@
         <v>5</v>
       </c>
       <c r="W37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X37">
         <v>6</v>
@@ -3703,7 +3703,7 @@
         <v>-1</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R38">
         <v>6</v>
@@ -3721,7 +3721,7 @@
         <v>8</v>
       </c>
       <c r="W38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X38">
         <v>8</v>
@@ -3780,7 +3780,7 @@
         <v>-1</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
         <v>8</v>
@@ -3798,7 +3798,7 @@
         <v>7</v>
       </c>
       <c r="W39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X39">
         <v>7</v>
@@ -3857,7 +3857,7 @@
         <v>-1</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R40">
         <v>5</v>
@@ -3934,7 +3934,7 @@
         <v>-1</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R41">
         <v>7</v>
@@ -4011,7 +4011,7 @@
         <v>-1</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R42">
         <v>7</v>
@@ -4088,7 +4088,7 @@
         <v>-1</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R43">
         <v>8</v>
@@ -4337,19 +4337,19 @@
         <v>41</v>
       </c>
       <c r="D7">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>100</v>
+        <v>97.56</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="H7">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/3ALCM - Estadisticos 20221.xlsx
+++ b/grupos/3ALCM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="179">
   <si>
     <t>Materia</t>
   </si>
@@ -203,10 +203,10 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Caballero Rosas María Teresa</t>
+  </si>
+  <si>
     <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
-    <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
     <t>Avila Coronado Julieta</t>
@@ -1079,10 +1079,10 @@
         <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
         <v>8</v>
@@ -1097,10 +1097,10 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>8</v>
@@ -1156,10 +1156,10 @@
         <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="Q5">
         <v>9</v>
@@ -1177,7 +1177,7 @@
         <v>7</v>
       </c>
       <c r="V5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W5">
         <v>10</v>
@@ -1233,10 +1233,10 @@
         <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
         <v>8</v>
@@ -1251,7 +1251,7 @@
         <v>9</v>
       </c>
       <c r="U6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V6">
         <v>8</v>
@@ -1310,10 +1310,10 @@
         <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
         <v>10</v>
@@ -1387,10 +1387,10 @@
         <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
         <v>9</v>
@@ -1405,7 +1405,7 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -1464,10 +1464,10 @@
         <v>5</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1541,10 +1541,10 @@
         <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
         <v>9</v>
@@ -1559,7 +1559,7 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V10">
         <v>8</v>
@@ -1618,10 +1618,10 @@
         <v>8</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
         <v>10</v>
@@ -1636,7 +1636,7 @@
         <v>9</v>
       </c>
       <c r="U11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V11">
         <v>8</v>
@@ -1695,10 +1695,10 @@
         <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
         <v>8</v>
@@ -1772,10 +1772,10 @@
         <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
         <v>8</v>
@@ -1790,7 +1790,7 @@
         <v>9</v>
       </c>
       <c r="U13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V13">
         <v>9</v>
@@ -1849,10 +1849,10 @@
         <v>8</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="Q14">
         <v>7</v>
@@ -1870,7 +1870,7 @@
         <v>5</v>
       </c>
       <c r="V14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W14">
         <v>9</v>
@@ -1926,10 +1926,10 @@
         <v>9</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q15">
         <v>8</v>
@@ -1944,7 +1944,7 @@
         <v>9</v>
       </c>
       <c r="U15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V15">
         <v>5</v>
@@ -2003,10 +2003,10 @@
         <v>9</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -2021,7 +2021,7 @@
         <v>9</v>
       </c>
       <c r="U16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V16">
         <v>8</v>
@@ -2080,10 +2080,10 @@
         <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
         <v>10</v>
@@ -2101,7 +2101,7 @@
         <v>7</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>10</v>
@@ -2157,10 +2157,10 @@
         <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
         <v>10</v>
@@ -2234,10 +2234,10 @@
         <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
         <v>9</v>
@@ -2252,7 +2252,7 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V19">
         <v>7</v>
@@ -2311,10 +2311,10 @@
         <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
         <v>8</v>
@@ -2329,7 +2329,7 @@
         <v>9</v>
       </c>
       <c r="U20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>7</v>
@@ -2388,10 +2388,10 @@
         <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
         <v>9</v>
@@ -2406,7 +2406,7 @@
         <v>9</v>
       </c>
       <c r="U21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V21">
         <v>8</v>
@@ -2465,10 +2465,10 @@
         <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
         <v>10</v>
@@ -2542,10 +2542,10 @@
         <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
         <v>10</v>
@@ -2619,10 +2619,10 @@
         <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
         <v>10</v>
@@ -2637,7 +2637,7 @@
         <v>10</v>
       </c>
       <c r="U24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V24">
         <v>8</v>
@@ -2696,10 +2696,10 @@
         <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
         <v>10</v>
@@ -2773,10 +2773,10 @@
         <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
         <v>9</v>
@@ -2794,7 +2794,7 @@
         <v>9</v>
       </c>
       <c r="V26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W26">
         <v>10</v>
@@ -2850,10 +2850,10 @@
         <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
         <v>10</v>
@@ -2927,10 +2927,10 @@
         <v>8</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
         <v>9</v>
@@ -2945,7 +2945,7 @@
         <v>9</v>
       </c>
       <c r="U28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V28">
         <v>8</v>
@@ -3004,10 +3004,10 @@
         <v>9</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
         <v>10</v>
@@ -3081,10 +3081,10 @@
         <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
         <v>9</v>
@@ -3099,7 +3099,7 @@
         <v>10</v>
       </c>
       <c r="U30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V30">
         <v>9</v>
@@ -3158,10 +3158,10 @@
         <v>9</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q31">
         <v>9</v>
@@ -3176,7 +3176,7 @@
         <v>9</v>
       </c>
       <c r="U31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V31">
         <v>8</v>
@@ -3235,10 +3235,10 @@
         <v>9</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
         <v>9</v>
@@ -3312,10 +3312,10 @@
         <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
         <v>10</v>
@@ -3389,10 +3389,10 @@
         <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
         <v>10</v>
@@ -3466,10 +3466,10 @@
         <v>9</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q35">
         <v>9</v>
@@ -3484,7 +3484,7 @@
         <v>9</v>
       </c>
       <c r="U35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V35">
         <v>8</v>
@@ -3543,10 +3543,10 @@
         <v>10</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q36">
         <v>9</v>
@@ -3561,7 +3561,7 @@
         <v>10</v>
       </c>
       <c r="U36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V36">
         <v>9</v>
@@ -3620,10 +3620,10 @@
         <v>7</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q37">
         <v>8</v>
@@ -3697,10 +3697,10 @@
         <v>9</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q38">
         <v>6</v>
@@ -3715,7 +3715,7 @@
         <v>9</v>
       </c>
       <c r="U38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V38">
         <v>8</v>
@@ -3774,10 +3774,10 @@
         <v>9</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q39">
         <v>10</v>
@@ -3792,7 +3792,7 @@
         <v>9</v>
       </c>
       <c r="U39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V39">
         <v>7</v>
@@ -3851,10 +3851,10 @@
         <v>8</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q40">
         <v>9</v>
@@ -3869,7 +3869,7 @@
         <v>9</v>
       </c>
       <c r="U40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V40">
         <v>7</v>
@@ -3928,10 +3928,10 @@
         <v>9</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q41">
         <v>9</v>
@@ -3946,7 +3946,7 @@
         <v>9</v>
       </c>
       <c r="U41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V41">
         <v>8</v>
@@ -4005,10 +4005,10 @@
         <v>9</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q42">
         <v>10</v>
@@ -4082,10 +4082,10 @@
         <v>9</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q43">
         <v>9</v>
@@ -4100,7 +4100,7 @@
         <v>9</v>
       </c>
       <c r="U43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V43">
         <v>8</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
@@ -4177,19 +4177,19 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>51.22</v>
+        <v>87.8</v>
       </c>
       <c r="G2">
-        <v>48.78</v>
+        <v>12.2</v>
       </c>
       <c r="H2">
-        <v>6.1</v>
+        <v>8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4200,7 +4200,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
@@ -4221,7 +4221,7 @@
         <v>7.32</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>6.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5124,7 +5124,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5156,22 +5156,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920262</v>
+        <v>21330051920081</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5179,22 +5179,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920262</v>
+        <v>21330051920081</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5217,7 +5217,7 @@
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5240,7 +5240,7 @@
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5248,19 +5248,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920251</v>
+        <v>21330051920252</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
         <v>61</v>
@@ -5271,366 +5271,24 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920253</v>
+        <v>21330051920262</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D7" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
         <v>61</v>
       </c>
       <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920256</v>
-      </c>
-      <c r="B8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" t="s">
-        <v>114</v>
-      </c>
-      <c r="D8" t="s">
-        <v>144</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>61</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920257</v>
-      </c>
-      <c r="B9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" t="s">
-        <v>115</v>
-      </c>
-      <c r="D9" t="s">
-        <v>145</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920081</v>
-      </c>
-      <c r="B10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" t="s">
-        <v>117</v>
-      </c>
-      <c r="D10" t="s">
-        <v>148</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>61</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920263</v>
-      </c>
-      <c r="B11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D11" t="s">
-        <v>142</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>61</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920264</v>
-      </c>
-      <c r="B12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" t="s">
-        <v>120</v>
-      </c>
-      <c r="D12" t="s">
-        <v>150</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>61</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920267</v>
-      </c>
-      <c r="B13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" t="s">
-        <v>152</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>61</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920088</v>
-      </c>
-      <c r="B14" t="s">
-        <v>87</v>
-      </c>
-      <c r="C14" t="s">
-        <v>122</v>
-      </c>
-      <c r="D14" t="s">
-        <v>154</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920358</v>
-      </c>
-      <c r="B15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" t="s">
-        <v>123</v>
-      </c>
-      <c r="D15" t="s">
-        <v>155</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920361</v>
-      </c>
-      <c r="B16" t="s">
-        <v>95</v>
-      </c>
-      <c r="C16" t="s">
-        <v>103</v>
-      </c>
-      <c r="D16" t="s">
-        <v>163</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>61</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920362</v>
-      </c>
-      <c r="B17" t="s">
-        <v>97</v>
-      </c>
-      <c r="C17" t="s">
-        <v>129</v>
-      </c>
-      <c r="D17" t="s">
-        <v>165</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>61</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920280</v>
-      </c>
-      <c r="B18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C18" t="s">
-        <v>77</v>
-      </c>
-      <c r="D18" t="s">
-        <v>171</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>61</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920284</v>
-      </c>
-      <c r="B19" t="s">
-        <v>105</v>
-      </c>
-      <c r="C19" t="s">
-        <v>135</v>
-      </c>
-      <c r="D19" t="s">
-        <v>173</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>61</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920285</v>
-      </c>
-      <c r="B20" t="s">
-        <v>106</v>
-      </c>
-      <c r="C20" t="s">
-        <v>94</v>
-      </c>
-      <c r="D20" t="s">
-        <v>174</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>61</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920286</v>
-      </c>
-      <c r="B21" t="s">
-        <v>107</v>
-      </c>
-      <c r="C21" t="s">
-        <v>93</v>
-      </c>
-      <c r="D21" t="s">
-        <v>175</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>61</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20330051920358</v>
-      </c>
-      <c r="B22" t="s">
-        <v>108</v>
-      </c>
-      <c r="C22" t="s">
-        <v>136</v>
-      </c>
-      <c r="D22" t="s">
-        <v>176</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>61</v>
-      </c>
-      <c r="G22">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ALCM - Estadisticos 20221.xlsx
+++ b/grupos/3ALCM - Estadisticos 20221.xlsx
@@ -1091,7 +1091,7 @@
         <v>6</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -1168,7 +1168,7 @@
         <v>6</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -1186,7 +1186,7 @@
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1245,7 +1245,7 @@
         <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>9</v>
@@ -1263,7 +1263,7 @@
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1322,7 +1322,7 @@
         <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -1399,7 +1399,7 @@
         <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -1476,7 +1476,7 @@
         <v>5</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T9">
         <v>5</v>
@@ -1553,7 +1553,7 @@
         <v>7</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>10</v>
@@ -1630,7 +1630,7 @@
         <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>9</v>
@@ -1707,7 +1707,7 @@
         <v>8</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>10</v>
@@ -1784,7 +1784,7 @@
         <v>6</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>9</v>
@@ -1861,7 +1861,7 @@
         <v>6</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
         <v>9</v>
@@ -1938,7 +1938,7 @@
         <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>9</v>
@@ -2015,7 +2015,7 @@
         <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
         <v>9</v>
@@ -2092,7 +2092,7 @@
         <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>10</v>
@@ -2169,7 +2169,7 @@
         <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>10</v>
@@ -2246,7 +2246,7 @@
         <v>7</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
         <v>10</v>
@@ -2323,7 +2323,7 @@
         <v>7</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
         <v>9</v>
@@ -2400,7 +2400,7 @@
         <v>9</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>9</v>
@@ -2477,7 +2477,7 @@
         <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>10</v>
@@ -2554,7 +2554,7 @@
         <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>10</v>
@@ -2631,7 +2631,7 @@
         <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -2708,7 +2708,7 @@
         <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2785,7 +2785,7 @@
         <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>10</v>
@@ -2862,7 +2862,7 @@
         <v>9</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>9</v>
@@ -2939,7 +2939,7 @@
         <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>9</v>
@@ -3016,7 +3016,7 @@
         <v>8</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>9</v>
@@ -3093,7 +3093,7 @@
         <v>8</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>10</v>
@@ -3170,7 +3170,7 @@
         <v>9</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>9</v>
@@ -3247,7 +3247,7 @@
         <v>9</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>9</v>
@@ -3324,7 +3324,7 @@
         <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -3401,7 +3401,7 @@
         <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>10</v>
@@ -3478,7 +3478,7 @@
         <v>9</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
         <v>9</v>
@@ -3555,7 +3555,7 @@
         <v>8</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
         <v>10</v>
@@ -3632,7 +3632,7 @@
         <v>7</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T37">
         <v>8</v>
@@ -3650,7 +3650,7 @@
         <v>6</v>
       </c>
       <c r="Y37">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3709,7 +3709,7 @@
         <v>6</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T38">
         <v>9</v>
@@ -3727,7 +3727,7 @@
         <v>8</v>
       </c>
       <c r="Y38">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3786,7 +3786,7 @@
         <v>8</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T39">
         <v>9</v>
@@ -3804,7 +3804,7 @@
         <v>7</v>
       </c>
       <c r="Y39">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3863,7 +3863,7 @@
         <v>5</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T40">
         <v>9</v>
@@ -3940,7 +3940,7 @@
         <v>7</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T41">
         <v>9</v>
@@ -4017,7 +4017,7 @@
         <v>7</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T42">
         <v>9</v>
@@ -4094,7 +4094,7 @@
         <v>8</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T43">
         <v>9</v>
@@ -4285,7 +4285,7 @@
         <v>2.44</v>
       </c>
       <c r="H5">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="I5">
         <v>0</v>
